--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>67,350.00</t>
+          <t>66,900.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63,033.00</t>
+          <t>62,605.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,550.00</t>
+          <t>66,100.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>66,350.00</t>
+          <t>65,900.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 11/10/2569 เวลา 09:15 น. (ครั้งที่ 1)</t>
+          <t>อัปเดตเมื่อ: 14/10/2569 เวลา 13:12 น. (ครั้งที่ 12)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,900.00</t>
+          <t>66,800.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,605.00</t>
+          <t>62,510.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,100.00</t>
+          <t>66,000.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,900.00</t>
+          <t>65,800.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 14/10/2569 เวลา 13:12 น. (ครั้งที่ 12)</t>
+          <t>อัปเดตเมื่อ: 14/10/2569 เวลา 13:52 น. (ครั้งที่ 14)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,800.00</t>
+          <t>66,850.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,510.00</t>
+          <t>62,558.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,000.00</t>
+          <t>66,050.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,800.00</t>
+          <t>65,850.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 14/10/2569 เวลา 13:52 น. (ครั้งที่ 14)</t>
+          <t>อัปเดตเมื่อ: 14/10/2569 เวลา 15:10 น. (ครั้งที่ 17)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,850.00</t>
+          <t>66,750.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,558.00</t>
+          <t>62,463.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,050.00</t>
+          <t>65,950.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,850.00</t>
+          <t>65,750.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 14/10/2569 เวลา 15:10 น. (ครั้งที่ 17)</t>
+          <t>อัปเดตเมื่อ: 14/10/2569 เวลา 15:46 น. (ครั้งที่ 19)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,750.00</t>
+          <t>66,650.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,463.00</t>
+          <t>62,368.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65,950.00</t>
+          <t>65,850.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,750.00</t>
+          <t>65,650.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 14/10/2569 เวลา 15:46 น. (ครั้งที่ 19)</t>
+          <t>อัปเดตเมื่อ: 15/10/2569 เวลา 12:34 น. (ครั้งที่ 10)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,650.00</t>
+          <t>66,550.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,368.00</t>
+          <t>62,273.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65,850.00</t>
+          <t>65,750.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,650.00</t>
+          <t>65,550.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 15/10/2569 เวลา 12:34 น. (ครั้งที่ 10)</t>
+          <t>อัปเดตเมื่อ: 15/10/2569 เวลา 14:05 น. (ครั้งที่ 14)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,550.00</t>
+          <t>66,700.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,273.00</t>
+          <t>62,415.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65,750.00</t>
+          <t>65,900.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,550.00</t>
+          <t>65,700.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 15/10/2569 เวลา 14:05 น. (ครั้งที่ 14)</t>
+          <t>อัปเดตเมื่อ: 15/10/2569 เวลา 15:24 น. (ครั้งที่ 17)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,700.00</t>
+          <t>66,750.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,415.00</t>
+          <t>62,463.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65,900.00</t>
+          <t>65,950.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,700.00</t>
+          <t>65,750.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 15/10/2569 เวลา 15:24 น. (ครั้งที่ 17)</t>
+          <t>อัปเดตเมื่อ: 15/10/2569 เวลา 16:22 น. (ครั้งที่ 18)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,750.00</t>
+          <t>66,800.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,463.00</t>
+          <t>62,510.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65,950.00</t>
+          <t>66,000.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,750.00</t>
+          <t>65,800.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 15/10/2569 เวลา 16:22 น. (ครั้งที่ 18)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 09:03 น. (ครั้งที่ 1)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,800.00</t>
+          <t>67,050.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,510.00</t>
+          <t>62,748.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,000.00</t>
+          <t>66,250.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,800.00</t>
+          <t>66,050.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 09:03 น. (ครั้งที่ 1)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 09:57 น. (ครั้งที่ 4)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>67,050.00</t>
+          <t>67,000.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,748.00</t>
+          <t>62,700.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,250.00</t>
+          <t>66,200.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>66,050.00</t>
+          <t>66,000.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 09:57 น. (ครั้งที่ 4)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 10:18 น. (ครั้งที่ 5)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 10:18 น. (ครั้งที่ 5)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 10:51 น. (ครั้งที่ 9)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>67,000.00</t>
+          <t>67,050.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,700.00</t>
+          <t>62,748.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,200.00</t>
+          <t>66,250.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>66,000.00</t>
+          <t>66,050.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 10:51 น. (ครั้งที่ 9)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 10:58 น. (ครั้งที่ 10)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>67,050.00</t>
+          <t>67,000.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,748.00</t>
+          <t>62,700.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,250.00</t>
+          <t>66,200.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>66,050.00</t>
+          <t>66,000.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 10:58 น. (ครั้งที่ 10)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 11:48 น. (ครั้งที่ 11)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>67,000.00</t>
+          <t>66,950.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,700.00</t>
+          <t>62,653.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,200.00</t>
+          <t>66,150.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>66,000.00</t>
+          <t>65,950.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 11:48 น. (ครั้งที่ 11)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 12:09 น. (ครั้งที่ 12)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,950.00</t>
+          <t>66,900.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,653.00</t>
+          <t>62,605.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,150.00</t>
+          <t>66,100.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,950.00</t>
+          <t>65,900.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 12:09 น. (ครั้งที่ 12)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 12:46 น. (ครั้งที่ 13)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 12:46 น. (ครั้งที่ 13)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 13:13 น. (ครั้งที่ 15)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,900.00</t>
+          <t>66,950.00</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,605.00</t>
+          <t>62,653.00</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,100.00</t>
+          <t>66,150.00</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,900.00</t>
+          <t>65,950.00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 13:13 น. (ครั้งที่ 15)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 13:34 น. (ครั้งที่ 16)</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -1,112 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\พุทเจริญสุข2\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_56BD4964D40B0DD58375A78864CECB3648A98D61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
-  <si>
-    <t>รูปพรรณ ขาย</t>
-  </si>
-  <si>
-    <t>66,950.00</t>
-  </si>
-  <si>
-    <t>ตารางการเติมข้อมูลต่อเดือน</t>
-  </si>
-  <si>
-    <t>ตารางการเติมข้อมูลต่อปี</t>
-  </si>
-  <si>
-    <t>รูปพรรณ รับ</t>
-  </si>
-  <si>
-    <t>62,653.00</t>
-  </si>
-  <si>
-    <t>เวลาอัปเดต</t>
-  </si>
-  <si>
-    <t>พรรณ ขาย</t>
-  </si>
-  <si>
-    <t>พรรณ ซื้อ</t>
-  </si>
-  <si>
-    <t>แท่ง ขาย</t>
-  </si>
-  <si>
-    <t>แท่ง ซื้อ</t>
-  </si>
-  <si>
-    <t>ส่วนต่าง พรรณ</t>
-  </si>
-  <si>
-    <t>ส่วนต่าง แท่ง</t>
-  </si>
-  <si>
-    <t>เดือน</t>
-  </si>
-  <si>
-    <t>ทองแท่ง ขาย</t>
-  </si>
-  <si>
-    <t>66,150.00</t>
-  </si>
-  <si>
-    <t>2026-10-16 15:21:58</t>
-  </si>
-  <si>
-    <t>ทองแท่ง รับ</t>
-  </si>
-  <si>
-    <t>65,950.00</t>
-  </si>
-  <si>
-    <t>อัปเดตเมื่อ: 16/10/2569 เวลา 15:15 น. (ครั้งที่ 18)</t>
-  </si>
-  <si>
-    <t>4,297.00</t>
-  </si>
-  <si>
-    <t>200.00</t>
-  </si>
-  <si>
-    <t>ปี</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -125,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -427,166 +407,246 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U9"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="19.19921875" customWidth="1"/>
-    <col min="6" max="6" width="8.796875" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="19.796875" customWidth="1"/>
-    <col min="13" max="13" width="14.8984375" customWidth="1"/>
-    <col min="14" max="14" width="15.5" customWidth="1"/>
-    <col min="20" max="20" width="12.19921875" customWidth="1"/>
-    <col min="21" max="21" width="12.3984375" customWidth="1"/>
+    <col width="19.19921875" customWidth="1" min="1" max="1"/>
+    <col width="8.796875" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="19.796875" customWidth="1" min="8" max="8"/>
+    <col width="14.8984375" customWidth="1" min="13" max="13"/>
+    <col width="15.5" customWidth="1" min="14" max="14"/>
+    <col width="12.19921875" customWidth="1" min="20" max="20"/>
+    <col width="12.3984375" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" t="s">
-        <v>10</v>
-      </c>
-      <c r="T2" t="s">
-        <v>11</v>
-      </c>
-      <c r="U2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>รูปพรรณ ขายออก</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>66,950.00</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ตารางการเติมข้อมูลต่อเดือน</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ตารางการเติมข้อมูลต่อปี</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>รูปพรรณ รับซื้อ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>62,653.00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>เวลาอัปเดต</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>พรรณ ขาย</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>พรรณ ซื้อ</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>แท่ง ขาย</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>แท่ง ซื้อ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ส่วนต่าง พรรณ</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ส่วนต่าง แท่ง</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>เดือน</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>พรรณ ขาย</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>พรรณ ซื้อ</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>แท่ง ขาย</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>แท่ง ซื้อ</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ส่วนต่าง พรรณ</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>ส่วนต่าง แท่ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ทองแท่ง ขายออก</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>66,150.00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:21:58</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>66950</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>62653</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>66150</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>65950</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>4297</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" t="s">
-        <v>12</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ทองแท่ง รับซื้อ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>65,950.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>เวลาอัปเดต</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 15:15 น. (ครั้งที่ 18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ส่วนต่าง พรรณ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4,297.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ส่วนต่าง แท่ง</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ปี</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>พรรณ ขาย</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>พรรณ ซื้อ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>แท่ง ขาย</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>แท่ง ซื้อ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ส่วนต่าง พรรณ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ส่วนต่าง แท่ง</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -433,7 +433,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,950.00</t>
+          <t>67,000.00</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,653.00</t>
+          <t>62,700.00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,150.00</t>
+          <t>66,200.00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -572,8 +572,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,950.00</t>
-        </is>
+          <t>66,000.00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30:32</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>67000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>62700</v>
+      </c>
+      <c r="K4" t="n">
+        <v>66200</v>
+      </c>
+      <c r="L4" t="n">
+        <v>66000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4300</v>
+      </c>
+      <c r="N4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +607,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 15:15 น. (ครั้งที่ 18)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 16:05 น. (ครั้งที่ 19)</t>
         </is>
       </c>
     </row>
@@ -596,7 +619,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4,297.00</t>
+          <t>4,300.00</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -433,7 +433,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>67,000.00</t>
+          <t>66,950.00</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,700.00</t>
+          <t>62,653.00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,200.00</t>
+          <t>66,150.00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>66,000.00</t>
+          <t>65,950.00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,8 +607,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 16:05 น. (ครั้งที่ 19)</t>
-        </is>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 16:35 น. (ครั้งที่ 20)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00:38</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>66950</v>
+      </c>
+      <c r="J5" t="n">
+        <v>62653</v>
+      </c>
+      <c r="K5" t="n">
+        <v>66150</v>
+      </c>
+      <c r="L5" t="n">
+        <v>65950</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4297</v>
+      </c>
+      <c r="N5" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="6">
@@ -619,7 +642,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4,300.00</t>
+          <t>4,297.00</t>
         </is>
       </c>
     </row>

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -433,7 +433,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>66,950.00</t>
+          <t>66,900.00</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62,653.00</t>
+          <t>62,605.00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66,150.00</t>
+          <t>66,100.00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65,950.00</t>
+          <t>65,900.00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 16:35 น. (ครั้งที่ 20)</t>
+          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 17:14 น. (ครั้งที่ 23)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -642,8 +642,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4,297.00</t>
-        </is>
+          <t>4,295.00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:30:32</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>66900</v>
+      </c>
+      <c r="J6" t="n">
+        <v>62605</v>
+      </c>
+      <c r="K6" t="n">
+        <v>66100</v>
+      </c>
+      <c r="L6" t="n">
+        <v>65900</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4295</v>
+      </c>
+      <c r="N6" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="7">

--- a/controller.xlsx
+++ b/controller.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อัปเดตเมื่อ: 16/10/2569 เวลา 17:14 น. (ครั้งที่ 23)</t>
+          <t>อัปเดตเมื่อ: 17/10/2569 เวลา 09:02 น. (ครั้งที่ 1)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
